--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10320"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBADD9B-FB66-444A-8FF3-823BE20605B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C9BF87-D6AE-704A-8022-FC1536F2588C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17896" windowHeight="11776" xr2:uid="{10ECA6D9-0F72-49C3-BB32-C1036777A9B7}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Building</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Floor 03</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>9:30 AM - 10:00 AM</t>
   </si>
   <si>
@@ -231,9 +228,6 @@
     <t>Floor 10</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>8:30 AM - 9:30 AM</t>
   </si>
   <si>
@@ -331,6 +325,12 @@
   </si>
   <si>
     <t>Bobbie Gaskin (SPD), Jen Seeley (SPD), Andy Tulloch (tulloca@ccf.org) (SCM Materials), Chris Orourek (ED admin)</t>
+  </si>
+  <si>
+    <t>Team A</t>
+  </si>
+  <si>
+    <t>Team B</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -525,9 +525,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,46 +1203,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77645D5B-2357-42B1-801B-E3F15014E9A1}">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.86328125" customWidth="1"/>
-    <col min="4" max="4" width="28.1328125" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" customWidth="1"/>
-    <col min="6" max="6" width="25.1328125" customWidth="1"/>
-    <col min="7" max="7" width="104.73046875" customWidth="1"/>
-    <col min="8" max="8" width="25.86328125" customWidth="1"/>
-    <col min="10" max="10" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.9140625" customWidth="1"/>
+    <col min="4" max="4" width="28.11328125" customWidth="1"/>
+    <col min="5" max="5" width="11.8359375" customWidth="1"/>
+    <col min="6" max="6" width="25.15234375" customWidth="1"/>
+    <col min="7" max="7" width="104.79296875" customWidth="1"/>
+    <col min="8" max="8" width="25.828125" customWidth="1"/>
+    <col min="10" max="10" width="20.4453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.66015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1254,251 +1251,251 @@
       <c r="C2" s="2">
         <v>10</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>46111</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>24</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>46111</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>46111</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2">
         <v>7</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>46111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A6" s="15" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>7</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>46112</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A7" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C7" s="2">
         <v>15</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>46112</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C8" s="2">
         <v>19</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>46112</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="G8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C9" s="2">
         <v>30</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>46112</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C10" s="2">
         <v>38</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>46112</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A11" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C11" s="2">
         <v>147</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>46112</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
-        <v>22</v>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -1506,277 +1503,277 @@
       <c r="C12" s="2">
         <v>118</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>46112</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A13" s="15" t="s">
-        <v>22</v>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2">
         <v>174</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>46113</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
-        <v>22</v>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2">
         <v>97</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>46113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A15" s="15" t="s">
-        <v>22</v>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2">
         <v>58</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>46113</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="5" t="s">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A16" s="15" t="s">
+      <c r="B16" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C16" s="2">
         <v>67</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>46112</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A17" s="15" t="s">
-        <v>52</v>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2">
         <v>25</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>46112</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="G17" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A18" s="15" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2">
         <v>21</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>46112</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A19" s="15" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="2">
         <v>42</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>46112</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A20" s="15" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2">
         <v>27</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>46112</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A21" s="15" t="s">
-        <v>52</v>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2">
         <v>5</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>46112</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A22" s="15" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2">
         <v>7</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>46112</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A23" s="15" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>9</v>
@@ -1784,106 +1781,106 @@
       <c r="C23" s="2">
         <v>32</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>46112</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H23" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A24" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>13</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>46112</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A25" s="15" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2">
         <v>9</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>46113</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A26" s="15" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2">
         <v>14</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>46113</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="5" t="s">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
         <v>71</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A27" s="15" t="s">
-        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>9</v>
@@ -1891,116 +1888,116 @@
       <c r="C27" s="2">
         <v>29</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>46113</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J27" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="5" t="s">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J27" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="K27" s="20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A28" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="B28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2">
         <v>45</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <v>46113</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J28" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="K28" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="5" t="s">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="K28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A29" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2">
         <v>41</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13">
         <v>46113</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="K29" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="5" t="s">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J29" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A30" s="16" t="s">
-        <v>73</v>
-      </c>
       <c r="B30" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="6">
         <v>25</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13">
         <v>46113</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="E30" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="F30" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="H30" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
